--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487876_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487876_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.298999999999999</v>
+        <v>7.8513</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3681</v>
+        <v>6.8323</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.019</v>
       </c>
       <c r="G2" t="n">
         <v>6.1343</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.916</v>
+        <v>0.4683</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9968</v>
+        <v>0.461</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0809</v>
+        <v>0.0072</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5229</v>
+        <v>6.6254</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0846</v>
+        <v>4.8347</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4384</v>
+        <v>1.7907</v>
       </c>
       <c r="G3" t="n">
         <v>3.6143</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7157</v>
+        <v>0.3867</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6524</v>
+        <v>0.0977</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0633</v>
+        <v>0.2891</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5134</v>
+        <v>3.9738</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2659</v>
+        <v>1.9025</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2474</v>
+        <v>2.0713</v>
       </c>
       <c r="G4" t="n">
         <v>3.3263</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8084</v>
+        <v>0.2688</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5153</v>
+        <v>0.152</v>
       </c>
       <c r="U4" t="n">
-        <v>0.293</v>
+        <v>0.1169</v>
       </c>
       <c r="V4" t="n">
         <v>1.6275</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0083</v>
+        <v>3.457</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5626</v>
+        <v>1.6279</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4457</v>
+        <v>1.8292</v>
       </c>
       <c r="G5" t="n">
         <v>2.0429</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9467</v>
+        <v>0.3954</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0152</v>
+        <v>0.3987</v>
       </c>
       <c r="V5" t="n">
         <v>-0.23</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9016</v>
+        <v>3.1706</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6974</v>
+        <v>2.0545</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2042</v>
+        <v>1.1161</v>
       </c>
       <c r="G6" t="n">
         <v>2.0843</v>
@@ -922,13 +922,13 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0066</v>
+        <v>0.2756</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0621</v>
+        <v>0.4191</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0554</v>
+        <v>-0.1435</v>
       </c>
       <c r="V6" t="n">
         <v>-0.23</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CHACON CARNERO</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.729</v>
+        <v>1.2716</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5618</v>
+        <v>0.4282</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1672</v>
+        <v>0.8435</v>
       </c>
       <c r="G7" t="n">
-        <v>0.378</v>
+        <v>2.0454</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.292</v>
       </c>
       <c r="I7" t="n">
-        <v>0.378</v>
+        <v>2.3374</v>
       </c>
       <c r="J7" t="n">
-        <v>0.627</v>
+        <v>1.323</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0959</v>
       </c>
       <c r="L7" t="n">
-        <v>0.627</v>
+        <v>1.2271</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.249</v>
+        <v>0.7224</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3879</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.249</v>
+        <v>1.1104</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.3937</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1458</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.248</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7168</v>
+        <v>1.1688</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2148</v>
+        <v>-0.1469</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9315</v>
+        <v>1.3157</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0454</v>
+        <v>-0.2877</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.292</v>
+        <v>-1.8063</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3374</v>
+        <v>1.5186</v>
       </c>
       <c r="J8" t="n">
-        <v>1.323</v>
+        <v>-0.7693</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0959</v>
+        <v>-1.0346</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2271</v>
+        <v>0.2653</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7224</v>
+        <v>0.4816</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3879</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1104</v>
+        <v>1.2532</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1611</v>
+        <v>0.0621</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4972</v>
+        <v>0.0386</v>
       </c>
       <c r="U8" t="n">
-        <v>0.336</v>
+        <v>0.0235</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>J. CHACON CARNERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5743</v>
+        <v>0.729</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6827</v>
+        <v>0.5618</v>
       </c>
       <c r="F9" t="n">
-        <v>1.257</v>
+        <v>0.1672</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2877</v>
+        <v>0.378</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8063</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5186</v>
+        <v>0.378</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7693</v>
+        <v>0.627</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0346</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2653</v>
+        <v>0.627</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4816</v>
+        <v>-0.249</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2532</v>
+        <v>-0.249</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5324</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4972</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0352</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4133</v>
+        <v>0.5285</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2298</v>
+        <v>-0.3789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6431</v>
+        <v>0.9074</v>
       </c>
       <c r="G10" t="n">
         <v>3.8534</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6315</v>
+        <v>-0.5164</v>
       </c>
       <c r="T10" t="n">
-        <v>0.152</v>
+        <v>0.0029</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7835</v>
+        <v>-0.5193</v>
       </c>
       <c r="V10" t="n">
         <v>0.9376</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1202</v>
+        <v>-1.9955</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0657</v>
+        <v>-2.5977</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9455</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3361</v>
+        <v>-0.819</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6719000000000001</v>
+        <v>-2.6952</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.008</v>
+        <v>1.8761</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.9971</v>
+        <v>0.0507</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7292</v>
+        <v>-1.8213</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.7263</v>
+        <v>1.872</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.339</v>
+        <v>-0.8697</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0573</v>
+        <v>-0.8738</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2817</v>
+        <v>0.0041</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0812</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3647</v>
+        <v>-0.344</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4332</v>
+        <v>-0.2335</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2178</v>
+        <v>-2.1137</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5558</v>
+        <v>-4.0004</v>
       </c>
       <c r="F13" t="n">
-        <v>0.338</v>
+        <v>1.8868</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.819</v>
+        <v>-4.3361</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6952</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8761</v>
+        <v>-5.008</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0507</v>
+        <v>-3.9971</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8213</v>
+        <v>0.7292</v>
       </c>
       <c r="L13" t="n">
-        <v>1.872</v>
+        <v>-4.7263</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8697</v>
+        <v>-0.339</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8738</v>
+        <v>-0.0573</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0041</v>
+        <v>-0.2817</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5663</v>
+        <v>0.3712</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4978</v>
+        <v>0.3745</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.474</v>
+        <v>24.8002</v>
       </c>
       <c r="E14" t="n">
-        <v>10.9006</v>
+        <v>11.227</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5733</v>
+        <v>13.5736</v>
       </c>
       <c r="G14" t="n">
         <v>18.8591</v>
@@ -1522,7 +1522,7 @@
         <v>19.5956</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7163</v>
+        <v>2.716300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>16.8794</v>
@@ -1546,13 +1546,13 @@
         <v>16.6494</v>
       </c>
       <c r="S14" t="n">
-        <v>1.305</v>
+        <v>1.631</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7435</v>
+        <v>1.0696</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5613000000000001</v>
+        <v>0.5616000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.2289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9516</v>
+        <v>3.708</v>
       </c>
       <c r="E15" t="n">
-        <v>4.214</v>
+        <v>3.9997</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2624</v>
+        <v>-0.2917</v>
       </c>
       <c r="G15" t="n">
         <v>3.2533</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0072</v>
+        <v>-0.2509</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3171</v>
+        <v>-0.5314</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3099</v>
+        <v>0.2806</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4462</v>
+        <v>0.7675</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6813</v>
+        <v>1.7169</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2351</v>
+        <v>-0.9494</v>
       </c>
       <c r="G16" t="n">
         <v>0.9370000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1554</v>
+        <v>0.4767</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3602</v>
+        <v>0.3958</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2048</v>
+        <v>0.0809</v>
       </c>
       <c r="V16" t="n">
         <v>-0.23</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3917</v>
+        <v>-0.2337</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3786</v>
+        <v>-0.2715</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0131</v>
+        <v>0.0378</v>
       </c>
       <c r="G17" t="n">
         <v>-1.003</v>
@@ -1780,13 +1780,13 @@
         <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7164</v>
+        <v>0.8744</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1363</v>
+        <v>0.2434</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.631</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9376</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3608</v>
+        <v>-2.4454</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3804</v>
+        <v>-2.7439</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9803</v>
+        <v>0.2985</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1596</v>
+        <v>-3.6715</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4177</v>
+        <v>-1.0875</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5773</v>
+        <v>-2.584</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2817</v>
+        <v>-1.9405</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0465</v>
+        <v>-0.4546</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2351</v>
+        <v>-1.4859</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4412</v>
+        <v>-1.731</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6288</v>
+        <v>-0.6329</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8124</v>
+        <v>-1.0981</v>
       </c>
       <c r="P18" t="n">
+        <v>1.8731</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>2.9137</v>
       </c>
       <c r="S18" t="n">
-        <v>0.777</v>
+        <v>-0.4171</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2297</v>
+        <v>-0.3467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4527</v>
+        <v>-0.0704</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7145</v>
+        <v>-2.8613</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4808</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2336</v>
+        <v>-1.3804</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6941</v>
@@ -1936,13 +1936,13 @@
         <v>0.2081</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1879</v>
+        <v>-0.3347</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3791</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1912</v>
+        <v>0.0444</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5185</v>
+        <v>-3.0036</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.494</v>
+        <v>-2.9939</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0245</v>
+        <v>-0.0097</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6715</v>
+        <v>-2.7228</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0875</v>
+        <v>-0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.584</v>
+        <v>-2.4158</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9405</v>
+        <v>-1.2817</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4546</v>
+        <v>-0.3926</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4859</v>
+        <v>-0.8891</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.731</v>
+        <v>-1.4411</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6329</v>
+        <v>0.0856</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0981</v>
+        <v>-1.5267</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8731</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9137</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4901</v>
+        <v>0.2166</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0967</v>
+        <v>0.242</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3934</v>
+        <v>-0.0254</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9822</v>
+        <v>-3.3149</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4226</v>
+        <v>-1.452</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5597</v>
+        <v>-1.8629</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7228</v>
+        <v>-1.1596</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.307</v>
+        <v>0.4177</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4158</v>
+        <v>-1.5773</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2817</v>
+        <v>1.2817</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3926</v>
+        <v>1.0465</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8891</v>
+        <v>0.2351</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4411</v>
+        <v>-2.4412</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0856</v>
+        <v>-0.6288</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5267</v>
+        <v>-1.8124</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6649</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.762</v>
+        <v>-0.1771</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1866</v>
+        <v>0.1582</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5754</v>
+        <v>-0.3353</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1675</v>
+        <v>-0.9376</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8234</v>
+        <v>-4.5988</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5706</v>
+        <v>-1.4635</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2528</v>
+        <v>-3.1354</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8954</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5337</v>
+        <v>-0.3091</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2075</v>
+        <v>-0.09</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3538</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6414</v>
+        <v>-5.25</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6111</v>
+        <v>-5.1825</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0303</v>
+        <v>-0.0675</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1716</v>
@@ -2248,13 +2248,13 @@
         <v>2.4974</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2649</v>
+        <v>0.1266</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3948</v>
+        <v>0.0339</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1299</v>
+        <v>0.0927</v>
       </c>
       <c r="V23" t="n">
         <v>0.4599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4392</v>
+        <v>-5.8129</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1305</v>
+        <v>-3.7019</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3087</v>
+        <v>-2.1111</v>
       </c>
       <c r="G24" t="n">
         <v>-5.7314</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7078</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1207</v>
+        <v>0.077</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.4739</v>
+        <v>-23.0451</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.5733</v>
+        <v>-13.5734</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.9005</v>
+        <v>-9.4718</v>
       </c>
       <c r="G25" t="n">
         <v>-18.8591</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5927</v>
+        <v>3.592699999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-22.4516</v>
@@ -2380,7 +2380,7 @@
         <v>0.7364000000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>6.308700000000001</v>
+        <v>6.3087</v>
       </c>
       <c r="L25" t="n">
         <v>-5.5723</v>
@@ -2404,13 +2404,13 @@
         <v>14.5684</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3048</v>
+        <v>0.1238</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5614999999999994</v>
+        <v>-0.5616</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7434000000000002</v>
+        <v>0.6855</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2291</v>
